--- a/SMAS - Excel File/SocialMediaPosts.xlsx
+++ b/SMAS - Excel File/SocialMediaPosts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMAS - Excel File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Youssef Elshemy\Documents\Projects\Reddit-Automation-System\SMAS - Excel File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153E6EBB-DFA2-4BCB-8471-15DC0B551C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EDD95E-602E-4CE8-B9A9-25E85E7F61FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34650" yWindow="5730" windowWidth="20400" windowHeight="8850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>PostID</t>
   </si>
@@ -79,32 +79,41 @@
     <t>LoginPassword(separated by commas)</t>
   </si>
   <si>
-    <t>Reddit,Twitter</t>
-  </si>
-  <si>
-    <t>Reddit000,uuuiii000</t>
-  </si>
-  <si>
-    <t>Grand_Win_9630,uiPathProject00</t>
-  </si>
-  <si>
-    <t>,uiPathProject00@gmail.com</t>
-  </si>
-  <si>
-    <t>u/Grand_Win_9630</t>
-  </si>
-  <si>
     <t>title</t>
   </si>
   <si>
-    <t>BODeBODeBODeBODe</t>
+    <t>Reddit,Twitter,Quora</t>
+  </si>
+  <si>
+    <t>,uiPathProject00@gmail.com,omoswaken@gmail.com</t>
+  </si>
+  <si>
+    <t>Reddit000,uuuiii000,!2Qwerty</t>
+  </si>
+  <si>
+    <t>Test TestTest Test Test Test Test Test Test Test</t>
+  </si>
+  <si>
+    <t>omoswaken@gmail.com</t>
+  </si>
+  <si>
+    <t>!2Qwerty</t>
+  </si>
+  <si>
+    <t>Quora</t>
+  </si>
+  <si>
+    <t>Bubbly_Annual_9724,uiPathProject00,</t>
+  </si>
+  <si>
+    <t>u/Bubbly_Annual_9724</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +125,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -173,10 +190,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -189,8 +207,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -493,17 +513,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.7265625" customWidth="1"/>
     <col min="3" max="3" width="33.26953125" customWidth="1"/>
     <col min="4" max="4" width="36.54296875" customWidth="1"/>
     <col min="5" max="5" width="32.26953125" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" customWidth="1"/>
+    <col min="6" max="6" width="23.81640625" customWidth="1"/>
     <col min="7" max="7" width="18.81640625" customWidth="1"/>
-    <col min="8" max="8" width="31.7265625" customWidth="1"/>
+    <col min="8" max="8" width="42.54296875" customWidth="1"/>
     <col min="9" max="9" width="26.7265625" customWidth="1"/>
     <col min="10" max="10" width="33.453125" customWidth="1"/>
     <col min="11" max="11" width="15.81640625" customWidth="1"/>
@@ -573,25 +593,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
@@ -607,16 +627,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="J3" t="s">
         <v>14</v>
@@ -625,8 +645,34 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{76F54877-E2D0-4EA0-896E-0C8C7AC54E98}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>